--- a/artfynd/A 54160-2020 artfynd.xlsx
+++ b/artfynd/A 54160-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127097176</v>
       </c>
       <c r="B2" t="n">
-        <v>98340</v>
+        <v>98415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54160-2020 artfynd.xlsx
+++ b/artfynd/A 54160-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127097176</v>
       </c>
       <c r="B2" t="n">
-        <v>98415</v>
+        <v>98421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54160-2020 artfynd.xlsx
+++ b/artfynd/A 54160-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127097176</v>
       </c>
       <c r="B2" t="n">
-        <v>98421</v>
+        <v>98422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54160-2020 artfynd.xlsx
+++ b/artfynd/A 54160-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127097176</v>
       </c>
       <c r="B2" t="n">
-        <v>98422</v>
+        <v>98426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54160-2020 artfynd.xlsx
+++ b/artfynd/A 54160-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127097176</v>
       </c>
       <c r="B2" t="n">
-        <v>98426</v>
+        <v>98427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54160-2020 artfynd.xlsx
+++ b/artfynd/A 54160-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127097176</v>
       </c>
       <c r="B2" t="n">
-        <v>98427</v>
+        <v>98429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54160-2020 artfynd.xlsx
+++ b/artfynd/A 54160-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127097176</v>
       </c>
       <c r="B2" t="n">
-        <v>98429</v>
+        <v>98435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54160-2020 artfynd.xlsx
+++ b/artfynd/A 54160-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127097176</v>
       </c>
       <c r="B2" t="n">
-        <v>98435</v>
+        <v>98438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54160-2020 artfynd.xlsx
+++ b/artfynd/A 54160-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127097176</v>
       </c>
       <c r="B2" t="n">
-        <v>98438</v>
+        <v>98446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
